--- a/klasemen 25_26/klasemen laliga.xlsx
+++ b/klasemen 25_26/klasemen laliga.xlsx
@@ -443,7 +443,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Barcelona (Y)</v>
+        <v>Barcelona</v>
       </c>
       <c r="C2">
         <v>28</v>
